--- a/testdata/realdata/ippools.xlsx
+++ b/testdata/realdata/ippools.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>使用中</t>
+          <t>在网</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>使用中</t>
+          <t>在网</t>
         </is>
       </c>
     </row>
@@ -540,7 +540,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>使用中</t>
+          <t>在网</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>使用中</t>
+          <t>在网</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>使用中</t>
+          <t>停用</t>
         </is>
       </c>
     </row>

--- a/testdata/realdata/ippools.xlsx
+++ b/testdata/realdata/ippools.xlsx
@@ -456,12 +456,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10.60.0.0/24</t>
+          <t>10.200.0.0/24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10.60.0.1</t>
+          <t>10.200.0.1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -471,7 +471,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>DEV-279116876-01</t>
+          <t>DEV-1603990225-01</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -488,12 +488,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10.61.0.0/24</t>
+          <t>10.201.0.0/24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>10.61.0.1</t>
+          <t>10.201.0.1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -503,7 +503,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>DEV-244077958-01</t>
+          <t>DEV-1727803072-01</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10.62.0.0/24</t>
+          <t>10.202.0.0/24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>10.62.0.1</t>
+          <t>10.202.0.1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -535,7 +535,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>DEV-244081515-01</t>
+          <t>DEV-1933473774-01</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -552,12 +552,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10.63.0.0/24</t>
+          <t>10.203.0.0/24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>10.63.0.1</t>
+          <t>10.203.0.1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>DEV-1727803072-01</t>
+          <t>DEV-2168737545-01</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -584,12 +584,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10.64.0.0/24</t>
+          <t>10.204.0.0/24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>10.64.0.1</t>
+          <t>10.204.0.1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>DEV-469656125-01</t>
+          <t>DEV-2289935762-01</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
